--- a/artfynd/A 50292-2021 artfynd.xlsx
+++ b/artfynd/A 50292-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50292-2021 artfynd.xlsx
+++ b/artfynd/A 50292-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2606,6 +2606,220 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126222594</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98343</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kullen, Kullen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>478598</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6556212</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Kvistbro</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126222624</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58021</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Baggetorp, Baggetorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>478598</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6556212</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Kvistbro</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50292-2021 artfynd.xlsx
+++ b/artfynd/A 50292-2021 artfynd.xlsx
@@ -2611,7 +2611,7 @@
         <v>126222594</v>
       </c>
       <c r="B17" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 50292-2021 artfynd.xlsx
+++ b/artfynd/A 50292-2021 artfynd.xlsx
@@ -2611,7 +2611,7 @@
         <v>126222594</v>
       </c>
       <c r="B17" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>126222624</v>
       </c>
       <c r="B18" t="n">
-        <v>58021</v>
+        <v>58025</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 50292-2021 artfynd.xlsx
+++ b/artfynd/A 50292-2021 artfynd.xlsx
@@ -2611,7 +2611,7 @@
         <v>126222594</v>
       </c>
       <c r="B17" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 50292-2021 artfynd.xlsx
+++ b/artfynd/A 50292-2021 artfynd.xlsx
@@ -2611,7 +2611,7 @@
         <v>126222594</v>
       </c>
       <c r="B17" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>126222624</v>
       </c>
       <c r="B18" t="n">
-        <v>58025</v>
+        <v>58027</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 50292-2021 artfynd.xlsx
+++ b/artfynd/A 50292-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2820,6 +2820,121 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131524677</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99023</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Baggetorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>478610</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6556170</v>
+      </c>
+      <c r="S19" t="n">
+        <v>84</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Kvistbro</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>T-Lek-0025</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2021-10-30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2021-10-30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Sara Stenman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50292-2021 artfynd.xlsx
+++ b/artfynd/A 50292-2021 artfynd.xlsx
@@ -2825,7 +2825,7 @@
         <v>131524677</v>
       </c>
       <c r="B19" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 50292-2021 artfynd.xlsx
+++ b/artfynd/A 50292-2021 artfynd.xlsx
@@ -2825,7 +2825,7 @@
         <v>131524677</v>
       </c>
       <c r="B19" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 50292-2021 artfynd.xlsx
+++ b/artfynd/A 50292-2021 artfynd.xlsx
@@ -2825,7 +2825,7 @@
         <v>131524677</v>
       </c>
       <c r="B19" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 50292-2021 artfynd.xlsx
+++ b/artfynd/A 50292-2021 artfynd.xlsx
@@ -2825,7 +2825,7 @@
         <v>131524677</v>
       </c>
       <c r="B19" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 50292-2021 artfynd.xlsx
+++ b/artfynd/A 50292-2021 artfynd.xlsx
@@ -2825,7 +2825,7 @@
         <v>131524677</v>
       </c>
       <c r="B19" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 50292-2021 artfynd.xlsx
+++ b/artfynd/A 50292-2021 artfynd.xlsx
@@ -2825,7 +2825,7 @@
         <v>131524677</v>
       </c>
       <c r="B19" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 50292-2021 artfynd.xlsx
+++ b/artfynd/A 50292-2021 artfynd.xlsx
@@ -2825,7 +2825,7 @@
         <v>131524677</v>
       </c>
       <c r="B19" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 50292-2021 artfynd.xlsx
+++ b/artfynd/A 50292-2021 artfynd.xlsx
@@ -2825,7 +2825,7 @@
         <v>131524677</v>
       </c>
       <c r="B19" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 50292-2021 artfynd.xlsx
+++ b/artfynd/A 50292-2021 artfynd.xlsx
@@ -2825,7 +2825,7 @@
         <v>131524677</v>
       </c>
       <c r="B19" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 50292-2021 artfynd.xlsx
+++ b/artfynd/A 50292-2021 artfynd.xlsx
@@ -2825,7 +2825,7 @@
         <v>131524677</v>
       </c>
       <c r="B19" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 50292-2021 artfynd.xlsx
+++ b/artfynd/A 50292-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,64 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55055381</v>
+        <v>97055107</v>
       </c>
       <c r="B2" t="n">
-        <v>56966</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102120</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödstrupig piplärka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anthus cervinus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pallas, 1811)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Baggetorp, Nrk</t>
+          <t>Hemsjöberget, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478539.4359462929</v>
+        <v>478538</v>
       </c>
       <c r="R2" t="n">
-        <v>6556219.266495869</v>
+        <v>6556046</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-09-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-09-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,27 +760,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kjell Ståhlberg</t>
+          <t>Rolf Wedding</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kjell Ståhlberg</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Rolf Wedding, Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62390257</v>
+        <v>97055108</v>
       </c>
       <c r="B3" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -814,41 +787,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Baggetorp 8750/2450, Nrk</t>
+          <t>Hemsjöberget, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478539.4359462929</v>
+        <v>478579</v>
       </c>
       <c r="R3" t="n">
-        <v>6556219.266495869</v>
+        <v>6556121</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,27 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1983-04-20</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1983-04-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ca 25</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,81 +861,68 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>Rolf Wedding</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Rolf Wedding, Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96911505</v>
+        <v>112231588</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2818</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Naturstig Baggetorp Lekebergs kommun, Nrk</t>
+          <t>Baggetorp, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478611.1190852095</v>
+        <v>478719</v>
       </c>
       <c r="R4" t="n">
-        <v>6556171.151443472</v>
+        <v>6556487</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1005,22 +946,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,77 +964,100 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # murken grov låga # Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sara Stenman</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sara Stenman</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96976791</v>
+        <v>112205187</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4363</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Baggetorp, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478566.8659228896</v>
+        <v>478587</v>
       </c>
       <c r="R5" t="n">
-        <v>6556344.804701482</v>
+        <v>6556137</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1130,27 +1084,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>några hundra plantor</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1170,7 +1109,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>äldre barrskog</t>
+          <t>i yta bökad av vildsvin</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1181,77 +1120,68 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Michael Andersson, Rolf Wedding</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96976975</v>
+        <v>96976858</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Baggetorp, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478635.2024014339</v>
+        <v>478614</v>
       </c>
       <c r="R6" t="n">
-        <v>6556158.190483694</v>
+        <v>6556243</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1281,57 +1211,23 @@
           <t>2021-11-03</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-11-03</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På mossigt granitblock.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>äldre barrskog</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Block (&gt; 200 mm)</t>
-        </is>
-      </c>
-      <c r="AN6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Rock (&gt; 200 mm) # mossigt granitblock, ca 1 meter i diameter</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1349,55 +1245,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96977039</v>
+        <v>112269209</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1405,13 +1292,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478624.9810476306</v>
+        <v>478539</v>
       </c>
       <c r="R7" t="n">
-        <v>6556168.508597264</v>
+        <v>6556219</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1435,22 +1322,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1459,19 +1336,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>äldre barrskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1481,64 +1347,55 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Michael Andersson, Rolf Wedding</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96977976</v>
+        <v>97055116</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Baggetorp, Nrk</t>
+          <t>Hemsjöberget, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478586.6705521682</v>
+        <v>478479</v>
       </c>
       <c r="R8" t="n">
-        <v>6556118.957577563</v>
+        <v>6556128</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1565,19 +1422,14 @@
           <t>2021-11-03</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-11-03</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>barkgnag</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1586,74 +1438,66 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Rolf Wedding</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Michael Andersson, Rolf Wedding</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Rolf Wedding, Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96976817</v>
+        <v>55055381</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58559</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>102120</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödstrupig piplärka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anthus cervinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Pallas, 1811)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1662,13 +1506,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478614.0910485122</v>
+        <v>478539</v>
       </c>
       <c r="R9" t="n">
-        <v>6556242.960346372</v>
+        <v>6556219</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1692,22 +1536,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
+          <t>2015-09-04</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
+          <t>2015-09-04</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1716,66 +1560,50 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>äldre barrskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Kjell Ståhlberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Michael Andersson, Rolf Wedding</t>
+          <t>Kjell Ståhlberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96976858</v>
+        <v>55055363</v>
       </c>
       <c r="B10" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>102977</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1787,23 +1615,22 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Baggetorp, Nrk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478614.0910485122</v>
+        <v>478539</v>
       </c>
       <c r="R10" t="n">
-        <v>6556242.960346372</v>
+        <v>6556219</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1827,22 +1654,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
+          <t>2015-09-04</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
+          <t>2015-09-04</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1853,78 +1680,64 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Kjell Ståhlberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Michael Andersson, Rolf Wedding</t>
+          <t>Kjell Ståhlberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96977984</v>
+        <v>126222624</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Baggetorp, Nrk</t>
+          <t>Baggetorp, Baggetorp, Nrk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478628.070419746</v>
+        <v>478598</v>
       </c>
       <c r="R11" t="n">
-        <v>6556169.517393919</v>
+        <v>6556212</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1948,22 +1761,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1972,74 +1785,75 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Michael Andersson, Rolf Wedding</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>97055108</v>
+        <v>112231491</v>
       </c>
       <c r="B12" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2810</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hemsjöberget, Nrk</t>
+          <t>Baggetorp, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478578.4560685809</v>
+        <v>478579</v>
       </c>
       <c r="R12" t="n">
-        <v>6556120.542806052</v>
+        <v>6556322</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2066,22 +1880,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2096,12 +1900,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Rolf Wedding</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Rolf Wedding, Michael Andersson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2112,65 +1916,64 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112269209</v>
+        <v>96911505</v>
       </c>
       <c r="B13" t="n">
-        <v>56477</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Baggetorp, Nrk</t>
+          <t>Naturstig Baggetorp Lekebergs kommun, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478539</v>
+        <v>478611</v>
       </c>
       <c r="R13" t="n">
-        <v>6556219</v>
+        <v>6556171</v>
       </c>
       <c r="S13" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2194,12 +1997,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2208,80 +2011,76 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Sara Stenman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Sara Stenman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112231491</v>
+        <v>96976791</v>
       </c>
       <c r="B14" t="n">
-        <v>56606</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Baggetorp, Nrk</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478579</v>
+        <v>478567</v>
       </c>
       <c r="R14" t="n">
-        <v>6556322</v>
+        <v>6556345</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2308,12 +2107,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2021-11-03</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>några hundra plantor</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2322,8 +2126,19 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2333,72 +2148,64 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Michael Andersson, Rolf Wedding</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112205187</v>
+        <v>96976817</v>
       </c>
       <c r="B15" t="n">
-        <v>90851</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4363</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Baggetorp, Nrk</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478586</v>
+        <v>478614</v>
       </c>
       <c r="R15" t="n">
-        <v>6556137</v>
+        <v>6556243</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2425,12 +2232,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2450,7 +2257,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>i yta bökad av vildsvin</t>
+          <t>äldre barrskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2461,65 +2268,72 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Michael Andersson, Rolf Wedding</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112231588</v>
+        <v>96976975</v>
       </c>
       <c r="B16" t="n">
-        <v>93381</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2818</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Baggetorp, Nrk</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478719</v>
+        <v>478635</v>
       </c>
       <c r="R16" t="n">
-        <v>6556487</v>
+        <v>6556158</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2546,12 +2360,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2021-11-03</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På mossigt granitblock.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2569,24 +2388,22 @@
           <t>Blåbärsbarrskog</t>
         </is>
       </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
+          <t>Block (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AN16" t="n">
+        <v>1</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # murken grov låga # Pinus sylvestris</t>
+          <t>1 substratenheter # Rock (&gt; 200 mm) # mossigt granitblock, ca 1 meter i diameter</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2597,21 +2414,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Rolf Wedding, Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126222594</v>
+        <v>96977039</v>
       </c>
       <c r="B17" t="n">
-        <v>98361</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2636,20 +2449,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kullen, Kullen, Nrk</t>
+          <t>Baggetorp, Nrk</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478598</v>
+        <v>478625</v>
       </c>
       <c r="R17" t="n">
-        <v>6556212</v>
+        <v>6556168</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2673,22 +2502,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:39</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:39</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2697,66 +2516,81 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Michael Andersson, Rolf Wedding</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126222624</v>
+        <v>96977976</v>
       </c>
       <c r="B18" t="n">
-        <v>58027</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Baggetorp, Baggetorp, Nrk</t>
+          <t>Baggetorp, Nrk</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478598</v>
+        <v>478586</v>
       </c>
       <c r="R18" t="n">
-        <v>6556212</v>
+        <v>6556119</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2780,22 +2614,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>12:48</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:48</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2804,28 +2628,34 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Michael Andersson, Rolf Wedding</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131524677</v>
+        <v>96977984</v>
       </c>
       <c r="B19" t="n">
-        <v>99054</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2850,29 +2680,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Baggetorp, Nrk</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478610</v>
+        <v>478628</v>
       </c>
       <c r="R19" t="n">
-        <v>6556170</v>
+        <v>6556169</v>
       </c>
       <c r="S19" t="n">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2894,19 +2719,14 @@
           <t>Kvistbro</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>T-Lek-0025</t>
-        </is>
-      </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2915,25 +2735,355 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Michael Andersson, Rolf Wedding</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126221575</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kullen, Kullen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>478598</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6556212</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Kvistbro</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131524677</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Baggetorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>478610</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6556170</v>
+      </c>
+      <c r="S21" t="n">
+        <v>84</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Kvistbro</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>T-Lek-0025</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2021-10-30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2021-10-30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
           <t>Sofia Lund</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
+      <c r="AX21" t="inlineStr">
         <is>
           <t>Sara Stenman</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr">
+      <c r="AY21" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>62390257</v>
+      </c>
+      <c r="B22" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Baggetorp 8750/2450, Nrk</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>478539</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6556219</v>
+      </c>
+      <c r="S22" t="n">
+        <v>50</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Kvistbro</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>1983-04-20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>1983-04-20</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>ca 25</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
